--- a/dataset_t6_grouped/results2/G2/G2_T1448_W0038F0001T0006Z000C1N6_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G2/G2_T1448_W0038F0001T0006Z000C1N6_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>56.46868614806345</v>
+        <v>9.176161499060312</v>
       </c>
       <c r="D2" t="n">
-        <v>57.15852195619444</v>
+        <v>9.288259817881597</v>
       </c>
       <c r="E2" t="n">
-        <v>13.66618043741622</v>
+        <v>2.220754321080135</v>
       </c>
       <c r="F2" t="n">
-        <v>12.94592437510408</v>
+        <v>2.103712710954414</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>50.89866199196793</v>
+        <v>8.271032573694788</v>
       </c>
       <c r="D3" t="n">
-        <v>53.04524380897948</v>
+        <v>8.619852118959166</v>
       </c>
       <c r="E3" t="n">
-        <v>13.66618043741622</v>
+        <v>2.220754321080135</v>
       </c>
       <c r="F3" t="n">
-        <v>12.94592437510408</v>
+        <v>2.103712710954414</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>43.80806132347917</v>
+        <v>7.118809965065366</v>
       </c>
       <c r="D4" t="n">
-        <v>45.89715991484803</v>
+        <v>7.458288486162805</v>
       </c>
       <c r="E4" t="n">
-        <v>13.66618043741622</v>
+        <v>2.220754321080135</v>
       </c>
       <c r="F4" t="n">
-        <v>12.94592437510408</v>
+        <v>2.103712710954414</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>60.59931457645157</v>
+        <v>9.84738861867338</v>
       </c>
       <c r="D5" t="n">
-        <v>62.84425849966425</v>
+        <v>10.21219200619544</v>
       </c>
       <c r="E5" t="n">
-        <v>13.66618043741622</v>
+        <v>2.220754321080135</v>
       </c>
       <c r="F5" t="n">
-        <v>12.94592437510408</v>
+        <v>2.103712710954414</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>37.67566093732444</v>
+        <v>6.122294902315223</v>
       </c>
       <c r="D6" t="n">
-        <v>38.99362559341916</v>
+        <v>6.336464158930614</v>
       </c>
       <c r="E6" t="n">
-        <v>13.66618043741622</v>
+        <v>2.220754321080135</v>
       </c>
       <c r="F6" t="n">
-        <v>12.94592437510408</v>
+        <v>2.103712710954414</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>33.32315421182017</v>
+        <v>5.415012559420777</v>
       </c>
       <c r="D7" t="n">
-        <v>35.35849133420839</v>
+        <v>5.745754841808863</v>
       </c>
       <c r="E7" t="n">
-        <v>13.66618043741622</v>
+        <v>2.220754321080135</v>
       </c>
       <c r="F7" t="n">
-        <v>12.94592437510408</v>
+        <v>2.103712710954414</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>26.43248326620699</v>
+        <v>4.295278530758637</v>
       </c>
       <c r="D8" t="n">
-        <v>28.25550004823071</v>
+        <v>4.591518757837491</v>
       </c>
       <c r="E8" t="n">
-        <v>13.66618043741622</v>
+        <v>2.220754321080135</v>
       </c>
       <c r="F8" t="n">
-        <v>12.94592437510408</v>
+        <v>2.103712710954414</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>16.55954046747236</v>
+        <v>2.690925325964259</v>
       </c>
       <c r="D9" t="n">
-        <v>18.50886709186562</v>
+        <v>3.007690902428163</v>
       </c>
       <c r="E9" t="n">
-        <v>13.66618043741622</v>
+        <v>2.220754321080135</v>
       </c>
       <c r="F9" t="n">
-        <v>12.94592437510408</v>
+        <v>2.103712710954414</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>48.68875639282457</v>
+        <v>7.911922913833992</v>
       </c>
       <c r="D10" t="n">
-        <v>47.20426671038216</v>
+        <v>7.670693340437101</v>
       </c>
       <c r="E10" t="n">
-        <v>13.66618043741622</v>
+        <v>2.220754321080135</v>
       </c>
       <c r="F10" t="n">
-        <v>12.94592437510408</v>
+        <v>2.103712710954414</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>21.44198855907914</v>
+        <v>3.48432314085036</v>
       </c>
       <c r="D11" t="n">
-        <v>22.80034101957803</v>
+        <v>3.705055415681431</v>
       </c>
       <c r="E11" t="n">
-        <v>13.66618043741622</v>
+        <v>2.220754321080135</v>
       </c>
       <c r="F11" t="n">
-        <v>12.94592437510408</v>
+        <v>2.103712710954414</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>50.69935142874751</v>
+        <v>8.238644607171471</v>
       </c>
       <c r="D12" t="n">
-        <v>52.0958306445078</v>
+        <v>8.465572479732518</v>
       </c>
       <c r="E12" t="n">
-        <v>13.66618043741622</v>
+        <v>2.220754321080135</v>
       </c>
       <c r="F12" t="n">
-        <v>12.94592437510408</v>
+        <v>2.103712710954414</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>49.06471378908621</v>
+        <v>7.973015990726509</v>
       </c>
       <c r="D13" t="n">
-        <v>50.09347527111505</v>
+        <v>8.140189731556196</v>
       </c>
       <c r="E13" t="n">
-        <v>13.66618043741622</v>
+        <v>2.220754321080135</v>
       </c>
       <c r="F13" t="n">
-        <v>12.94592437510408</v>
+        <v>2.103712710954414</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>27.24134271408489</v>
+        <v>4.426718191038796</v>
       </c>
       <c r="D14" t="n">
-        <v>25.74078741712913</v>
+        <v>4.182877955283485</v>
       </c>
       <c r="E14" t="n">
-        <v>13.66618043741622</v>
+        <v>2.220754321080135</v>
       </c>
       <c r="F14" t="n">
-        <v>12.94592437510408</v>
+        <v>2.103712710954414</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>51.26976671723609</v>
+        <v>8.331337091550864</v>
       </c>
       <c r="D15" t="n">
-        <v>49.06107053344985</v>
+        <v>7.972423961685601</v>
       </c>
       <c r="E15" t="n">
-        <v>13.66618043741622</v>
+        <v>2.220754321080135</v>
       </c>
       <c r="F15" t="n">
-        <v>12.94592437510408</v>
+        <v>2.103712710954414</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>58.64143741994213</v>
+        <v>9.529233580740597</v>
       </c>
       <c r="D16" t="n">
-        <v>56.46369836732401</v>
+        <v>9.175350984690153</v>
       </c>
       <c r="E16" t="n">
-        <v>13.66618043741622</v>
+        <v>2.220754321080135</v>
       </c>
       <c r="F16" t="n">
-        <v>12.94592437510408</v>
+        <v>2.103712710954414</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>49.82569152012184</v>
+        <v>8.096674872019801</v>
       </c>
       <c r="D17" t="n">
-        <v>47.6239569861681</v>
+        <v>7.738893010252317</v>
       </c>
       <c r="E17" t="n">
-        <v>13.66618043741622</v>
+        <v>2.220754321080135</v>
       </c>
       <c r="F17" t="n">
-        <v>12.94592437510408</v>
+        <v>2.103712710954414</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>55.68560322471328</v>
+        <v>9.048910524015909</v>
       </c>
       <c r="D18" t="n">
-        <v>53.43212229168546</v>
+        <v>8.682719872398888</v>
       </c>
       <c r="E18" t="n">
-        <v>13.66618043741622</v>
+        <v>2.220754321080135</v>
       </c>
       <c r="F18" t="n">
-        <v>12.94592437510408</v>
+        <v>2.103712710954414</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1024,16 +1024,16 @@
         <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>48.31986205014955</v>
+        <v>7.851977583149301</v>
       </c>
       <c r="D19" t="n">
-        <v>46.57229028507827</v>
+        <v>7.56799717132522</v>
       </c>
       <c r="E19" t="n">
-        <v>13.66618043741622</v>
+        <v>2.220754321080135</v>
       </c>
       <c r="F19" t="n">
-        <v>12.94592437510408</v>
+        <v>2.103712710954414</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1056,16 +1056,16 @@
         <v>19</v>
       </c>
       <c r="C20" t="n">
-        <v>67.52492042666594</v>
+        <v>10.97279956933322</v>
       </c>
       <c r="D20" t="n">
-        <v>65.24675432777077</v>
+        <v>10.60259757826275</v>
       </c>
       <c r="E20" t="n">
-        <v>13.66618043741622</v>
+        <v>2.220754321080135</v>
       </c>
       <c r="F20" t="n">
-        <v>12.94592437510408</v>
+        <v>2.103712710954414</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1088,16 +1088,16 @@
         <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>58.19145281829616</v>
+        <v>9.456111082973125</v>
       </c>
       <c r="D21" t="n">
-        <v>56.58445202635813</v>
+        <v>9.194973454283197</v>
       </c>
       <c r="E21" t="n">
-        <v>13.66618043741622</v>
+        <v>2.220754321080135</v>
       </c>
       <c r="F21" t="n">
-        <v>12.94592437510408</v>
+        <v>2.103712710954414</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
